--- a/STARTREK.xlsx
+++ b/STARTREK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A336B-63B5-460B-BE0C-8CF2DA721630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4A104E-7468-4BA8-BC9D-A9949368A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STARTREK" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10664" uniqueCount="3815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10671" uniqueCount="3822">
   <si>
     <t>id</t>
   </si>
@@ -11468,6 +11468,27 @@
   </si>
   <si>
     <t>E²</t>
+  </si>
+  <si>
+    <t>2903.9</t>
+  </si>
+  <si>
+    <t>2011.7</t>
+  </si>
+  <si>
+    <t>2122.4</t>
+  </si>
+  <si>
+    <t>3019.4</t>
+  </si>
+  <si>
+    <t>1213.72</t>
+  </si>
+  <si>
+    <t>2654.9</t>
+  </si>
+  <si>
+    <t>2179.3</t>
   </si>
 </sst>
 </file>
@@ -11844,21 +11865,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R991"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="46.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.140625" customWidth="1"/>
-    <col min="12" max="12" width="51.28515625" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="37.140625" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.265625" customWidth="1"/>
+    <col min="6" max="6" width="46.73046875" customWidth="1"/>
+    <col min="8" max="8" width="22.265625" customWidth="1"/>
+    <col min="9" max="9" width="22.265625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.1328125" customWidth="1"/>
+    <col min="12" max="12" width="51.265625" customWidth="1"/>
+    <col min="14" max="14" width="15.1328125" customWidth="1"/>
+    <col min="15" max="15" width="37.1328125" customWidth="1"/>
+    <col min="16" max="16" width="17.265625" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11911,7 +11932,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -11958,7 +11979,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -12005,7 +12026,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -12052,7 +12073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -12099,7 +12120,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -12146,7 +12167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -12193,7 +12214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -12240,7 +12261,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -12287,7 +12308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -12334,7 +12355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -12381,7 +12402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -12428,7 +12449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -12475,7 +12496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -12522,7 +12543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -12569,7 +12590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -12616,7 +12637,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -12663,7 +12684,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -12710,7 +12731,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -12757,7 +12778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -12804,7 +12825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -12851,7 +12872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -12898,7 +12919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -12945,7 +12966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -12992,7 +13013,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -13039,7 +13060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -13086,7 +13107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -13133,7 +13154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -13180,7 +13201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>131</v>
       </c>
@@ -13227,7 +13248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>135</v>
       </c>
@@ -13274,7 +13295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -13321,7 +13342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -13368,7 +13389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -13415,7 +13436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -13462,7 +13483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -13509,7 +13530,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>159</v>
       </c>
@@ -13556,7 +13577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>163</v>
       </c>
@@ -13603,7 +13624,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>167</v>
       </c>
@@ -13650,7 +13671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>171</v>
       </c>
@@ -13697,7 +13718,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -13744,7 +13765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>179</v>
       </c>
@@ -13791,7 +13812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>183</v>
       </c>
@@ -13838,7 +13859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -13885,7 +13906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -13932,7 +13953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>195</v>
       </c>
@@ -13979,7 +14000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>199</v>
       </c>
@@ -14026,7 +14047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -14073,7 +14094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>207</v>
       </c>
@@ -14120,7 +14141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>211</v>
       </c>
@@ -14167,7 +14188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>215</v>
       </c>
@@ -14214,7 +14235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>219</v>
       </c>
@@ -14261,7 +14282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>223</v>
       </c>
@@ -14308,7 +14329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>227</v>
       </c>
@@ -14355,7 +14376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -14402,7 +14423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>236</v>
       </c>
@@ -14449,7 +14470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>240</v>
       </c>
@@ -14496,7 +14517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>244</v>
       </c>
@@ -14543,7 +14564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>248</v>
       </c>
@@ -14590,7 +14611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>252</v>
       </c>
@@ -14637,7 +14658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>256</v>
       </c>
@@ -14684,7 +14705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>260</v>
       </c>
@@ -14731,7 +14752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>264</v>
       </c>
@@ -14778,7 +14799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>268</v>
       </c>
@@ -14825,7 +14846,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>272</v>
       </c>
@@ -14872,7 +14893,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>276</v>
       </c>
@@ -14919,7 +14940,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>280</v>
       </c>
@@ -14966,7 +14987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>284</v>
       </c>
@@ -15013,7 +15034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>288</v>
       </c>
@@ -15060,7 +15081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>292</v>
       </c>
@@ -15107,7 +15128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>296</v>
       </c>
@@ -15154,7 +15175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>300</v>
       </c>
@@ -15201,7 +15222,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>304</v>
       </c>
@@ -15248,7 +15269,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>308</v>
       </c>
@@ -15295,7 +15316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>312</v>
       </c>
@@ -15342,7 +15363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>315</v>
       </c>
@@ -15389,7 +15410,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>319</v>
       </c>
@@ -15436,7 +15457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>323</v>
       </c>
@@ -15483,7 +15504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>327</v>
       </c>
@@ -15530,7 +15551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>332</v>
       </c>
@@ -15577,7 +15598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>336</v>
       </c>
@@ -15624,7 +15645,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>340</v>
       </c>
@@ -15671,7 +15692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>344</v>
       </c>
@@ -15718,7 +15739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>348</v>
       </c>
@@ -15765,7 +15786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>352</v>
       </c>
@@ -15812,7 +15833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>356</v>
       </c>
@@ -15859,7 +15880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>360</v>
       </c>
@@ -15906,7 +15927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>364</v>
       </c>
@@ -15953,7 +15974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>368</v>
       </c>
@@ -16000,7 +16021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>372</v>
       </c>
@@ -16047,7 +16068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>376</v>
       </c>
@@ -16094,7 +16115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>380</v>
       </c>
@@ -16141,7 +16162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>384</v>
       </c>
@@ -16188,7 +16209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>388</v>
       </c>
@@ -16235,7 +16256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>392</v>
       </c>
@@ -16282,7 +16303,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>396</v>
       </c>
@@ -16329,7 +16350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>400</v>
       </c>
@@ -16376,7 +16397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>404</v>
       </c>
@@ -16423,7 +16444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>408</v>
       </c>
@@ -16470,7 +16491,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>412</v>
       </c>
@@ -16517,7 +16538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>416</v>
       </c>
@@ -16561,7 +16582,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>424</v>
       </c>
@@ -16611,7 +16632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>431</v>
       </c>
@@ -16661,7 +16682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>434</v>
       </c>
@@ -16712,7 +16733,7 @@
       </c>
       <c r="R103" s="2"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>438</v>
       </c>
@@ -16762,7 +16783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>441</v>
       </c>
@@ -16812,7 +16833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>444</v>
       </c>
@@ -16862,7 +16883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>447</v>
       </c>
@@ -16912,7 +16933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>451</v>
       </c>
@@ -16962,7 +16983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>455</v>
       </c>
@@ -17012,7 +17033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>458</v>
       </c>
@@ -17062,7 +17083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>461</v>
       </c>
@@ -17112,7 +17133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>464</v>
       </c>
@@ -17162,7 +17183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>467</v>
       </c>
@@ -17212,7 +17233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>471</v>
       </c>
@@ -17262,7 +17283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>474</v>
       </c>
@@ -17312,7 +17333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>477</v>
       </c>
@@ -17362,7 +17383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>483</v>
       </c>
@@ -17412,7 +17433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>487</v>
       </c>
@@ -17462,7 +17483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>491</v>
       </c>
@@ -17512,7 +17533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>495</v>
       </c>
@@ -17562,7 +17583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>498</v>
       </c>
@@ -17612,7 +17633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>502</v>
       </c>
@@ -17662,7 +17683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>505</v>
       </c>
@@ -17712,7 +17733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>509</v>
       </c>
@@ -17762,7 +17783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>512</v>
       </c>
@@ -17812,7 +17833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>515</v>
       </c>
@@ -17862,7 +17883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>518</v>
       </c>
@@ -17912,7 +17933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>522</v>
       </c>
@@ -17962,7 +17983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>526</v>
       </c>
@@ -18012,7 +18033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>530</v>
       </c>
@@ -18062,7 +18083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>537</v>
       </c>
@@ -18112,7 +18133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>541</v>
       </c>
@@ -18162,7 +18183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>545</v>
       </c>
@@ -18212,7 +18233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>549</v>
       </c>
@@ -18262,7 +18283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>553</v>
       </c>
@@ -18312,7 +18333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>557</v>
       </c>
@@ -18362,7 +18383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>561</v>
       </c>
@@ -18412,7 +18433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>565</v>
       </c>
@@ -18462,7 +18483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>569</v>
       </c>
@@ -18512,7 +18533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>573</v>
       </c>
@@ -18562,7 +18583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>579</v>
       </c>
@@ -18612,7 +18633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>583</v>
       </c>
@@ -18662,7 +18683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>587</v>
       </c>
@@ -18712,7 +18733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>591</v>
       </c>
@@ -18762,7 +18783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>595</v>
       </c>
@@ -18812,7 +18833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>599</v>
       </c>
@@ -18862,7 +18883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>603</v>
       </c>
@@ -18912,7 +18933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>607</v>
       </c>
@@ -18962,7 +18983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>611</v>
       </c>
@@ -19012,7 +19033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>615</v>
       </c>
@@ -19062,7 +19083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>620</v>
       </c>
@@ -19112,7 +19133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>624</v>
       </c>
@@ -19162,7 +19183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>628</v>
       </c>
@@ -19212,7 +19233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>631</v>
       </c>
@@ -19262,7 +19283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>635</v>
       </c>
@@ -19312,7 +19333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>638</v>
       </c>
@@ -19362,7 +19383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>642</v>
       </c>
@@ -19412,7 +19433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>646</v>
       </c>
@@ -19462,7 +19483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>650</v>
       </c>
@@ -19512,7 +19533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>654</v>
       </c>
@@ -19562,7 +19583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>660</v>
       </c>
@@ -19581,9 +19602,18 @@
       <c r="F161" t="s">
         <v>661</v>
       </c>
+      <c r="G161">
+        <v>60</v>
+      </c>
       <c r="H161" s="1">
         <v>46233</v>
       </c>
+      <c r="I161" s="4" t="s">
+        <v>3815</v>
+      </c>
+      <c r="J161">
+        <v>2262</v>
+      </c>
       <c r="K161" t="s">
         <v>21</v>
       </c>
@@ -19603,7 +19633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>663</v>
       </c>
@@ -19622,9 +19652,18 @@
       <c r="F162" t="s">
         <v>664</v>
       </c>
+      <c r="G162">
+        <v>48</v>
+      </c>
       <c r="H162" s="1">
         <v>46240</v>
       </c>
+      <c r="I162" s="4" t="s">
+        <v>3816</v>
+      </c>
+      <c r="J162">
+        <v>2262</v>
+      </c>
       <c r="K162" t="s">
         <v>21</v>
       </c>
@@ -19644,7 +19683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>666</v>
       </c>
@@ -19663,9 +19702,18 @@
       <c r="F163" t="s">
         <v>667</v>
       </c>
+      <c r="G163">
+        <v>51</v>
+      </c>
       <c r="H163" s="1">
         <v>46247</v>
       </c>
+      <c r="I163" s="4" t="s">
+        <v>3817</v>
+      </c>
+      <c r="J163">
+        <v>2262</v>
+      </c>
       <c r="K163" t="s">
         <v>21</v>
       </c>
@@ -19685,7 +19733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>669</v>
       </c>
@@ -19704,9 +19752,18 @@
       <c r="F164" t="s">
         <v>670</v>
       </c>
+      <c r="G164">
+        <v>55</v>
+      </c>
       <c r="H164" s="1">
         <v>46254</v>
       </c>
+      <c r="I164" s="4" t="s">
+        <v>3818</v>
+      </c>
+      <c r="J164">
+        <v>2262</v>
+      </c>
       <c r="K164" t="s">
         <v>21</v>
       </c>
@@ -19726,7 +19783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>672</v>
       </c>
@@ -19745,9 +19802,18 @@
       <c r="F165" t="s">
         <v>673</v>
       </c>
+      <c r="G165">
+        <v>57</v>
+      </c>
       <c r="H165" s="1">
         <v>46261</v>
       </c>
+      <c r="I165" s="4" t="s">
+        <v>3819</v>
+      </c>
+      <c r="J165">
+        <v>2262</v>
+      </c>
       <c r="K165" t="s">
         <v>21</v>
       </c>
@@ -19767,7 +19833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>675</v>
       </c>
@@ -19786,9 +19852,18 @@
       <c r="F166" t="s">
         <v>676</v>
       </c>
+      <c r="G166">
+        <v>45</v>
+      </c>
       <c r="H166" s="1">
         <v>46268</v>
       </c>
+      <c r="I166" s="4" t="s">
+        <v>3820</v>
+      </c>
+      <c r="J166">
+        <v>2262</v>
+      </c>
       <c r="K166" t="s">
         <v>21</v>
       </c>
@@ -19808,7 +19883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>678</v>
       </c>
@@ -19827,9 +19902,18 @@
       <c r="F167" t="s">
         <v>679</v>
       </c>
+      <c r="G167">
+        <v>63</v>
+      </c>
       <c r="H167" s="1">
         <v>46275</v>
       </c>
+      <c r="I167" s="4" t="s">
+        <v>3821</v>
+      </c>
+      <c r="J167">
+        <v>2262</v>
+      </c>
       <c r="K167" t="s">
         <v>21</v>
       </c>
@@ -19849,7 +19933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>681</v>
       </c>
@@ -19890,7 +19974,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>684</v>
       </c>
@@ -19931,7 +20015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>687</v>
       </c>
@@ -19963,7 +20047,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>691</v>
       </c>
@@ -19995,7 +20079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>694</v>
       </c>
@@ -20027,7 +20111,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>697</v>
       </c>
@@ -20059,7 +20143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>700</v>
       </c>
@@ -20091,7 +20175,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>703</v>
       </c>
@@ -20123,7 +20207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>706</v>
       </c>
@@ -20173,7 +20257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>713</v>
       </c>
@@ -20223,7 +20307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>717</v>
       </c>
@@ -20273,7 +20357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>721</v>
       </c>
@@ -20323,7 +20407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>725</v>
       </c>
@@ -20373,7 +20457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>729</v>
       </c>
@@ -20423,7 +20507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>733</v>
       </c>
@@ -20473,7 +20557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>737</v>
       </c>
@@ -20523,7 +20607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>741</v>
       </c>
@@ -20573,7 +20657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>744</v>
       </c>
@@ -20623,7 +20707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>748</v>
       </c>
@@ -20673,7 +20757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>752</v>
       </c>
@@ -20723,7 +20807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>756</v>
       </c>
@@ -20773,7 +20857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>760</v>
       </c>
@@ -20823,7 +20907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>764</v>
       </c>
@@ -20873,7 +20957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>768</v>
       </c>
@@ -20923,7 +21007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>772</v>
       </c>
@@ -20973,7 +21057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>776</v>
       </c>
@@ -21023,7 +21107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>780</v>
       </c>
@@ -21073,7 +21157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>784</v>
       </c>
@@ -21123,7 +21207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>789</v>
       </c>
@@ -21173,7 +21257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>793</v>
       </c>
@@ -21223,7 +21307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>797</v>
       </c>
@@ -21273,7 +21357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>801</v>
       </c>
@@ -21323,7 +21407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>805</v>
       </c>
@@ -21373,7 +21457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>809</v>
       </c>
@@ -21423,7 +21507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>812</v>
       </c>
@@ -21473,7 +21557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>816</v>
       </c>
@@ -21523,7 +21607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>820</v>
       </c>
@@ -21573,7 +21657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>825</v>
       </c>
@@ -21623,7 +21707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>830</v>
       </c>
@@ -21673,7 +21757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>834</v>
       </c>
@@ -21723,7 +21807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>838</v>
       </c>
@@ -21773,7 +21857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>841</v>
       </c>
@@ -21823,7 +21907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>844</v>
       </c>
@@ -21873,7 +21957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>847</v>
       </c>
@@ -21923,7 +22007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>851</v>
       </c>
@@ -21973,7 +22057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>854</v>
       </c>
@@ -22023,7 +22107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>858</v>
       </c>
@@ -22073,7 +22157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>861</v>
       </c>
@@ -22123,7 +22207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>865</v>
       </c>
@@ -22173,7 +22257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>868</v>
       </c>
@@ -22223,7 +22307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>872</v>
       </c>
@@ -22273,7 +22357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>876</v>
       </c>
@@ -22323,7 +22407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>880</v>
       </c>
@@ -22373,7 +22457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>884</v>
       </c>
@@ -22423,7 +22507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>888</v>
       </c>
@@ -22473,7 +22557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>892</v>
       </c>
@@ -22523,7 +22607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>896</v>
       </c>
@@ -22573,7 +22657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>899</v>
       </c>
@@ -22623,7 +22707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>903</v>
       </c>
@@ -22673,7 +22757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>907</v>
       </c>
@@ -22723,7 +22807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>910</v>
       </c>
@@ -22773,7 +22857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>914</v>
       </c>
@@ -22823,7 +22907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>917</v>
       </c>
@@ -22873,7 +22957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>920</v>
       </c>
@@ -22923,7 +23007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>925</v>
       </c>
@@ -22973,7 +23057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>928</v>
       </c>
@@ -23023,7 +23107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>932</v>
       </c>
@@ -23073,7 +23157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>936</v>
       </c>
@@ -23123,7 +23207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>939</v>
       </c>
@@ -23173,7 +23257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>943</v>
       </c>
@@ -23223,7 +23307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>947</v>
       </c>
@@ -23273,7 +23357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>950</v>
       </c>
@@ -23323,7 +23407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>953</v>
       </c>
@@ -23373,7 +23457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>957</v>
       </c>
@@ -23423,7 +23507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>960</v>
       </c>
@@ -23473,7 +23557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>964</v>
       </c>
@@ -23523,7 +23607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>968</v>
       </c>
@@ -23573,7 +23657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>971</v>
       </c>
@@ -23623,7 +23707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>975</v>
       </c>
@@ -23673,7 +23757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>978</v>
       </c>
@@ -23723,7 +23807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>982</v>
       </c>
@@ -23773,7 +23857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>986</v>
       </c>
@@ -23823,7 +23907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>990</v>
       </c>
@@ -23873,7 +23957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>994</v>
       </c>
@@ -23923,7 +24007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>998</v>
       </c>
@@ -23973,7 +24057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>1002</v>
       </c>
@@ -24023,7 +24107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>1006</v>
       </c>
@@ -24073,7 +24157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>1010</v>
       </c>
@@ -24123,7 +24207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>1018</v>
       </c>
@@ -24173,7 +24257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>1021</v>
       </c>
@@ -24223,7 +24307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>1025</v>
       </c>
@@ -24273,7 +24357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>1029</v>
       </c>
@@ -24323,7 +24407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>1032</v>
       </c>
@@ -24373,7 +24457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>1035</v>
       </c>
@@ -24423,7 +24507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>1039</v>
       </c>
@@ -24473,7 +24557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>1042</v>
       </c>
@@ -24523,7 +24607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>1045</v>
       </c>
@@ -24573,7 +24657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>1048</v>
       </c>
@@ -24623,7 +24707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>1052</v>
       </c>
@@ -24673,7 +24757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>1056</v>
       </c>
@@ -24723,7 +24807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>1059</v>
       </c>
@@ -24773,7 +24857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>1062</v>
       </c>
@@ -24823,7 +24907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>1065</v>
       </c>
@@ -24873,7 +24957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>1068</v>
       </c>
@@ -24923,7 +25007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>1074</v>
       </c>
@@ -24973,7 +25057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>1077</v>
       </c>
@@ -25023,7 +25107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>1080</v>
       </c>
@@ -25073,7 +25157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>1084</v>
       </c>
@@ -25123,7 +25207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>1088</v>
       </c>
@@ -25173,7 +25257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>1092</v>
       </c>
@@ -25220,7 +25304,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>1100</v>
       </c>
@@ -25267,7 +25351,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>1107</v>
       </c>
@@ -25314,7 +25398,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>1114</v>
       </c>
@@ -25361,7 +25445,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>1121</v>
       </c>
@@ -25408,7 +25492,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>1128</v>
       </c>
@@ -25455,7 +25539,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>1135</v>
       </c>
@@ -25505,7 +25589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>1142</v>
       </c>
@@ -25555,7 +25639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>1144</v>
       </c>
@@ -25605,7 +25689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>1148</v>
       </c>
@@ -25655,7 +25739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>1152</v>
       </c>
@@ -25705,7 +25789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>1156</v>
       </c>
@@ -25755,7 +25839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>1160</v>
       </c>
@@ -25805,7 +25889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>1164</v>
       </c>
@@ -25855,7 +25939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>1168</v>
       </c>
@@ -25905,7 +25989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>1172</v>
       </c>
@@ -25955,7 +26039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>1176</v>
       </c>
@@ -26005,7 +26089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>1180</v>
       </c>
@@ -26055,7 +26139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>1184</v>
       </c>
@@ -26105,7 +26189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>1188</v>
       </c>
@@ -26155,7 +26239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>1192</v>
       </c>
@@ -26205,7 +26289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>1195</v>
       </c>
@@ -26255,7 +26339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>1199</v>
       </c>
@@ -26305,7 +26389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>1203</v>
       </c>
@@ -26355,7 +26439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>1207</v>
       </c>
@@ -26405,7 +26489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>1211</v>
       </c>
@@ -26455,7 +26539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>1215</v>
       </c>
@@ -26505,7 +26589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>1219</v>
       </c>
@@ -26555,7 +26639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>1222</v>
       </c>
@@ -26605,7 +26689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>1226</v>
       </c>
@@ -26655,7 +26739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>1230</v>
       </c>
@@ -26705,7 +26789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>1234</v>
       </c>
@@ -26755,7 +26839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>1238</v>
       </c>
@@ -26805,7 +26889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>1244</v>
       </c>
@@ -26855,7 +26939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>1248</v>
       </c>
@@ -26905,7 +26989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>1252</v>
       </c>
@@ -26955,7 +27039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>1256</v>
       </c>
@@ -27005,7 +27089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>1260</v>
       </c>
@@ -27055,7 +27139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>1264</v>
       </c>
@@ -27105,7 +27189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>1268</v>
       </c>
@@ -27155,7 +27239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>1272</v>
       </c>
@@ -27205,7 +27289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>1276</v>
       </c>
@@ -27255,7 +27339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>1280</v>
       </c>
@@ -27305,7 +27389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>1284</v>
       </c>
@@ -27355,7 +27439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>1288</v>
       </c>
@@ -27405,7 +27489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>1292</v>
       </c>
@@ -27455,7 +27539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>1296</v>
       </c>
@@ -27505,7 +27589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>1300</v>
       </c>
@@ -27555,7 +27639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>1304</v>
       </c>
@@ -27605,7 +27689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>1308</v>
       </c>
@@ -27655,7 +27739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>1312</v>
       </c>
@@ -27705,7 +27789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>1316</v>
       </c>
@@ -27755,7 +27839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>1320</v>
       </c>
@@ -27805,7 +27889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>1324</v>
       </c>
@@ -27855,7 +27939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>1328</v>
       </c>
@@ -27905,7 +27989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>1334</v>
       </c>
@@ -27955,7 +28039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>1337</v>
       </c>
@@ -28005,7 +28089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>1341</v>
       </c>
@@ -28055,7 +28139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>1345</v>
       </c>
@@ -28105,7 +28189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>1349</v>
       </c>
@@ -28155,7 +28239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>1353</v>
       </c>
@@ -28205,7 +28289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>1357</v>
       </c>
@@ -28255,7 +28339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>1361</v>
       </c>
@@ -28305,7 +28389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>1365</v>
       </c>
@@ -28355,7 +28439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>1369</v>
       </c>
@@ -28405,7 +28489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>1373</v>
       </c>
@@ -28455,7 +28539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>1377</v>
       </c>
@@ -28505,7 +28589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>1381</v>
       </c>
@@ -28555,7 +28639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>1385</v>
       </c>
@@ -28605,7 +28689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>1389</v>
       </c>
@@ -28655,7 +28739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>1393</v>
       </c>
@@ -28705,7 +28789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>1397</v>
       </c>
@@ -28755,7 +28839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>1401</v>
       </c>
@@ -28805,7 +28889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>1405</v>
       </c>
@@ -28855,7 +28939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>1409</v>
       </c>
@@ -28905,7 +28989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>1413</v>
       </c>
@@ -28955,7 +29039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>1417</v>
       </c>
@@ -29005,7 +29089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>1421</v>
       </c>
@@ -29055,7 +29139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>1425</v>
       </c>
@@ -29105,7 +29189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>1430</v>
       </c>
@@ -29155,7 +29239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>1435</v>
       </c>
@@ -29205,7 +29289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>1441</v>
       </c>
@@ -29255,7 +29339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>1445</v>
       </c>
@@ -29305,7 +29389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>1449</v>
       </c>
@@ -29355,7 +29439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>1453</v>
       </c>
@@ -29405,7 +29489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>1457</v>
       </c>
@@ -29455,7 +29539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>1461</v>
       </c>
@@ -29505,7 +29589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>1465</v>
       </c>
@@ -29555,7 +29639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>1469</v>
       </c>
@@ -29605,7 +29689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>1473</v>
       </c>
@@ -29655,7 +29739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>1477</v>
       </c>
@@ -29705,7 +29789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>1481</v>
       </c>
@@ -29755,7 +29839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>1485</v>
       </c>
@@ -29805,7 +29889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>1489</v>
       </c>
@@ -29855,7 +29939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>1493</v>
       </c>
@@ -29905,7 +29989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>1496</v>
       </c>
@@ -29955,7 +30039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>1500</v>
       </c>
@@ -30005,7 +30089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>1504</v>
       </c>
@@ -30055,7 +30139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>1508</v>
       </c>
@@ -30105,7 +30189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>1512</v>
       </c>
@@ -30155,7 +30239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>1516</v>
       </c>
@@ -30205,7 +30289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>1520</v>
       </c>
@@ -30255,7 +30339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>1524</v>
       </c>
@@ -30305,7 +30389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>1529</v>
       </c>
@@ -30355,7 +30439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>1534</v>
       </c>
@@ -30405,7 +30489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>1539</v>
       </c>
@@ -30455,7 +30539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>1544</v>
       </c>
@@ -30505,7 +30589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>1550</v>
       </c>
@@ -30555,7 +30639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>1554</v>
       </c>
@@ -30605,7 +30689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>1558</v>
       </c>
@@ -30655,7 +30739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>1562</v>
       </c>
@@ -30705,7 +30789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>1566</v>
       </c>
@@ -30755,7 +30839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>1570</v>
       </c>
@@ -30805,7 +30889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>1575</v>
       </c>
@@ -30855,7 +30939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>1580</v>
       </c>
@@ -30905,7 +30989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>1585</v>
       </c>
@@ -30955,7 +31039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>1590</v>
       </c>
@@ -31005,7 +31089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>1595</v>
       </c>
@@ -31055,7 +31139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>1600</v>
       </c>
@@ -31105,7 +31189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>1605</v>
       </c>
@@ -31155,7 +31239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>1610</v>
       </c>
@@ -31205,7 +31289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>1615</v>
       </c>
@@ -31255,7 +31339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>1620</v>
       </c>
@@ -31305,7 +31389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="400" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>1625</v>
       </c>
@@ -31355,7 +31439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="401" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>1630</v>
       </c>
@@ -31405,7 +31489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>1635</v>
       </c>
@@ -31455,7 +31539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>1640</v>
       </c>
@@ -31505,7 +31589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>1645</v>
       </c>
@@ -31555,7 +31639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>1650</v>
       </c>
@@ -31605,7 +31689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>1655</v>
       </c>
@@ -31655,7 +31739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>1660</v>
       </c>
@@ -31705,7 +31789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>1665</v>
       </c>
@@ -31755,7 +31839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>1670</v>
       </c>
@@ -31805,7 +31889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>1677</v>
       </c>
@@ -31855,7 +31939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>1682</v>
       </c>
@@ -31905,7 +31989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>1687</v>
       </c>
@@ -31955,7 +32039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>1692</v>
       </c>
@@ -32005,7 +32089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>1697</v>
       </c>
@@ -32055,7 +32139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>1702</v>
       </c>
@@ -32105,7 +32189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>1707</v>
       </c>
@@ -32155,7 +32239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>1712</v>
       </c>
@@ -32205,7 +32289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>1717</v>
       </c>
@@ -32255,7 +32339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>1722</v>
       </c>
@@ -32305,7 +32389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>1727</v>
       </c>
@@ -32355,7 +32439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>1734</v>
       </c>
@@ -32405,7 +32489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>1736</v>
       </c>
@@ -32455,7 +32539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>1739</v>
       </c>
@@ -32505,7 +32589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>1743</v>
       </c>
@@ -32555,7 +32639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>1747</v>
       </c>
@@ -32605,7 +32689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>1752</v>
       </c>
@@ -32655,7 +32739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>1755</v>
       </c>
@@ -32705,7 +32789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>1760</v>
       </c>
@@ -32755,7 +32839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>1764</v>
       </c>
@@ -32805,7 +32889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>1769</v>
       </c>
@@ -32855,7 +32939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>1773</v>
       </c>
@@ -32905,7 +32989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>1777</v>
       </c>
@@ -32955,7 +33039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>1780</v>
       </c>
@@ -33005,7 +33089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>1785</v>
       </c>
@@ -33055,7 +33139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>1790</v>
       </c>
@@ -33105,7 +33189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>1793</v>
       </c>
@@ -33155,7 +33239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>1796</v>
       </c>
@@ -33205,7 +33289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>1801</v>
       </c>
@@ -33255,7 +33339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>1806</v>
       </c>
@@ -33305,7 +33389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>1809</v>
       </c>
@@ -33355,7 +33439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>1812</v>
       </c>
@@ -33405,7 +33489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>1817</v>
       </c>
@@ -33455,7 +33539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>1821</v>
       </c>
@@ -33505,7 +33589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>1826</v>
       </c>
@@ -33555,7 +33639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>1830</v>
       </c>
@@ -33605,7 +33689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>1835</v>
       </c>
@@ -33655,7 +33739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>1839</v>
       </c>
@@ -33705,7 +33789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>1844</v>
       </c>
@@ -33755,7 +33839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>1848</v>
       </c>
@@ -33805,7 +33889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>1853</v>
       </c>
@@ -33855,7 +33939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>1857</v>
       </c>
@@ -33905,7 +33989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>1862</v>
       </c>
@@ -33955,7 +34039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>1865</v>
       </c>
@@ -34005,7 +34089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>1868</v>
       </c>
@@ -34055,7 +34139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>1873</v>
       </c>
@@ -34105,7 +34189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>1880</v>
       </c>
@@ -34155,7 +34239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>1884</v>
       </c>
@@ -34205,7 +34289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>1889</v>
       </c>
@@ -34255,7 +34339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>1892</v>
       </c>
@@ -34305,7 +34389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>1895</v>
       </c>
@@ -34355,7 +34439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>1900</v>
       </c>
@@ -34405,7 +34489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>1905</v>
       </c>
@@ -34455,7 +34539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>1910</v>
       </c>
@@ -34505,7 +34589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>1914</v>
       </c>
@@ -34555,7 +34639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="465" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>1919</v>
       </c>
@@ -34605,7 +34689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="466" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>1923</v>
       </c>
@@ -34655,7 +34739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="467" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>1928</v>
       </c>
@@ -34705,7 +34789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="468" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>1932</v>
       </c>
@@ -34755,7 +34839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="469" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>1935</v>
       </c>
@@ -34805,7 +34889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="470" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>1940</v>
       </c>
@@ -34855,7 +34939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="471" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>1944</v>
       </c>
@@ -34905,7 +34989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="472" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>1949</v>
       </c>
@@ -34955,7 +35039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="473" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>1953</v>
       </c>
@@ -35005,7 +35089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="474" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>1958</v>
       </c>
@@ -35055,7 +35139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="475" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>1962</v>
       </c>
@@ -35105,7 +35189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="476" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>1966</v>
       </c>
@@ -35155,7 +35239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="477" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>1969</v>
       </c>
@@ -35205,7 +35289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="478" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>1973</v>
       </c>
@@ -35255,7 +35339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="479" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>1978</v>
       </c>
@@ -35305,7 +35389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="480" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>1983</v>
       </c>
@@ -35355,7 +35439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="481" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>1986</v>
       </c>
@@ -35405,7 +35489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="482" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>1990</v>
       </c>
@@ -35455,7 +35539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="483" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>1994</v>
       </c>
@@ -35505,7 +35589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="484" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>1999</v>
       </c>
@@ -35555,7 +35639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="485" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>2003</v>
       </c>
@@ -35605,7 +35689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="486" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>2008</v>
       </c>
@@ -35655,7 +35739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="487" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>2012</v>
       </c>
@@ -35705,7 +35789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="488" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>2017</v>
       </c>
@@ -35755,7 +35839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="489" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>2020</v>
       </c>
@@ -35805,7 +35889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="490" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>2025</v>
       </c>
@@ -35855,7 +35939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="491" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>2028</v>
       </c>
@@ -35905,7 +35989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="492" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>2033</v>
       </c>
@@ -35955,7 +36039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="493" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>2036</v>
       </c>
@@ -36005,7 +36089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="494" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>2041</v>
       </c>
@@ -36055,7 +36139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="495" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>2044</v>
       </c>
@@ -36105,7 +36189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="496" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>2049</v>
       </c>
@@ -36155,7 +36239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>2052</v>
       </c>
@@ -36205,7 +36289,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>2057</v>
       </c>
@@ -36255,7 +36339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>2060</v>
       </c>
@@ -36305,7 +36389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>2065</v>
       </c>
@@ -36355,7 +36439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>2070</v>
       </c>
@@ -36405,7 +36489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>2073</v>
       </c>
@@ -36455,7 +36539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>2076</v>
       </c>
@@ -36505,7 +36589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>2081</v>
       </c>
@@ -36555,7 +36639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>2084</v>
       </c>
@@ -36605,7 +36689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>2088</v>
       </c>
@@ -36655,7 +36739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>2091</v>
       </c>
@@ -36705,7 +36789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>2097</v>
       </c>
@@ -36755,7 +36839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>2100</v>
       </c>
@@ -36805,7 +36889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>2103</v>
       </c>
@@ -36855,7 +36939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>2106</v>
       </c>
@@ -36905,7 +36989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>2109</v>
       </c>
@@ -36955,7 +37039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>2112</v>
       </c>
@@ -37005,7 +37089,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>2115</v>
       </c>
@@ -37055,7 +37139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>2118</v>
       </c>
@@ -37105,7 +37189,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>2122</v>
       </c>
@@ -37149,7 +37233,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>2128</v>
       </c>
@@ -37199,7 +37283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>2132</v>
       </c>
@@ -37249,7 +37333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>2135</v>
       </c>
@@ -37299,7 +37383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>2139</v>
       </c>
@@ -37349,7 +37433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>2146</v>
       </c>
@@ -37399,7 +37483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>2148</v>
       </c>
@@ -37449,7 +37533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>2152</v>
       </c>
@@ -37499,7 +37583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>2155</v>
       </c>
@@ -37549,7 +37633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>2158</v>
       </c>
@@ -37599,7 +37683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>2162</v>
       </c>
@@ -37649,7 +37733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>2166</v>
       </c>
@@ -37699,7 +37783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>2170</v>
       </c>
@@ -37749,7 +37833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>2174</v>
       </c>
@@ -37799,7 +37883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>2178</v>
       </c>
@@ -37849,7 +37933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>2182</v>
       </c>
@@ -37899,7 +37983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>2185</v>
       </c>
@@ -37949,7 +38033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>2188</v>
       </c>
@@ -37999,7 +38083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>2192</v>
       </c>
@@ -38049,7 +38133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>2196</v>
       </c>
@@ -38099,7 +38183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>2199</v>
       </c>
@@ -38149,7 +38233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>2203</v>
       </c>
@@ -38199,7 +38283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>2206</v>
       </c>
@@ -38249,7 +38333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>2209</v>
       </c>
@@ -38299,7 +38383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>2213</v>
       </c>
@@ -38349,7 +38433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>2216</v>
       </c>
@@ -38399,7 +38483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>2220</v>
       </c>
@@ -38449,7 +38533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>2223</v>
       </c>
@@ -38499,7 +38583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>2227</v>
       </c>
@@ -38549,7 +38633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>2230</v>
       </c>
@@ -38599,7 +38683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>2234</v>
       </c>
@@ -38649,7 +38733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>2237</v>
       </c>
@@ -38699,7 +38783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>2241</v>
       </c>
@@ -38749,7 +38833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>2244</v>
       </c>
@@ -38799,7 +38883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>2247</v>
       </c>
@@ -38849,7 +38933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>2253</v>
       </c>
@@ -38899,7 +38983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>2257</v>
       </c>
@@ -38949,7 +39033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>2261</v>
       </c>
@@ -38999,7 +39083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>2265</v>
       </c>
@@ -39049,7 +39133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>2269</v>
       </c>
@@ -39099,7 +39183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>2275</v>
       </c>
@@ -39149,7 +39233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>2277</v>
       </c>
@@ -39199,7 +39283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>2280</v>
       </c>
@@ -39249,7 +39333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>2284</v>
       </c>
@@ -39299,7 +39383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>2287</v>
       </c>
@@ -39349,7 +39433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>2291</v>
       </c>
@@ -39399,7 +39483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>2294</v>
       </c>
@@ -39449,7 +39533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>2298</v>
       </c>
@@ -39499,7 +39583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>2301</v>
       </c>
@@ -39549,7 +39633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>2305</v>
       </c>
@@ -39599,7 +39683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>2308</v>
       </c>
@@ -39649,7 +39733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>2311</v>
       </c>
@@ -39699,7 +39783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>2315</v>
       </c>
@@ -39749,7 +39833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>2319</v>
       </c>
@@ -39799,7 +39883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>2323</v>
       </c>
@@ -39849,7 +39933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>2327</v>
       </c>
@@ -39899,7 +39983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>2330</v>
       </c>
@@ -39949,7 +40033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>2334</v>
       </c>
@@ -39999,7 +40083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>2337</v>
       </c>
@@ -40049,7 +40133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>2340</v>
       </c>
@@ -40099,7 +40183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>2344</v>
       </c>
@@ -40149,7 +40233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>2347</v>
       </c>
@@ -40199,7 +40283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>2351</v>
       </c>
@@ -40249,7 +40333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>2354</v>
       </c>
@@ -40299,7 +40383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>2357</v>
       </c>
@@ -40349,7 +40433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>2361</v>
       </c>
@@ -40399,7 +40483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>2365</v>
       </c>
@@ -40449,7 +40533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>2368</v>
       </c>
@@ -40499,7 +40583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>2372</v>
       </c>
@@ -40549,7 +40633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>2375</v>
       </c>
@@ -40599,7 +40683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>2379</v>
       </c>
@@ -40649,7 +40733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>2383</v>
       </c>
@@ -40699,7 +40783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>2387</v>
       </c>
@@ -40749,7 +40833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>2391</v>
       </c>
@@ -40799,7 +40883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>2395</v>
       </c>
@@ -40849,7 +40933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>2398</v>
       </c>
@@ -40899,7 +40983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>2401</v>
       </c>
@@ -40949,7 +41033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>2404</v>
       </c>
@@ -40999,7 +41083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>2407</v>
       </c>
@@ -41049,7 +41133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>2410</v>
       </c>
@@ -41099,7 +41183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>2414</v>
       </c>
@@ -41149,7 +41233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>2418</v>
       </c>
@@ -41199,7 +41283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>2422</v>
       </c>
@@ -41249,7 +41333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>2425</v>
       </c>
@@ -41299,7 +41383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>2428</v>
       </c>
@@ -41349,7 +41433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>2432</v>
       </c>
@@ -41399,7 +41483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>2436</v>
       </c>
@@ -41449,7 +41533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>2442</v>
       </c>
@@ -41499,7 +41583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>2446</v>
       </c>
@@ -41549,7 +41633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>2450</v>
       </c>
@@ -41599,7 +41683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>2454</v>
       </c>
@@ -41649,7 +41733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>2459</v>
       </c>
@@ -41699,7 +41783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>2463</v>
       </c>
@@ -41749,7 +41833,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>2467</v>
       </c>
@@ -41799,7 +41883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>2471</v>
       </c>
@@ -41849,7 +41933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>2475</v>
       </c>
@@ -41899,7 +41983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>2478</v>
       </c>
@@ -41949,7 +42033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>2481</v>
       </c>
@@ -41999,7 +42083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>2485</v>
       </c>
@@ -42049,7 +42133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>2489</v>
       </c>
@@ -42099,7 +42183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>2493</v>
       </c>
@@ -42149,7 +42233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>2496</v>
       </c>
@@ -42199,7 +42283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>2499</v>
       </c>
@@ -42249,7 +42333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>2502</v>
       </c>
@@ -42299,7 +42383,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>2506</v>
       </c>
@@ -42349,7 +42433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>2509</v>
       </c>
@@ -42399,7 +42483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>2513</v>
       </c>
@@ -42449,7 +42533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>2517</v>
       </c>
@@ -42493,7 +42577,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>2523</v>
       </c>
@@ -42543,7 +42627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>2526</v>
       </c>
@@ -42593,7 +42677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>2530</v>
       </c>
@@ -42643,7 +42727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>2533</v>
       </c>
@@ -42693,7 +42777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>2537</v>
       </c>
@@ -42743,7 +42827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>2540</v>
       </c>
@@ -42793,7 +42877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>2544</v>
       </c>
@@ -42843,7 +42927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>2548</v>
       </c>
@@ -42893,7 +42977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>2552</v>
       </c>
@@ -42943,7 +43027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>2555</v>
       </c>
@@ -42993,7 +43077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>2559</v>
       </c>
@@ -43043,7 +43127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>2563</v>
       </c>
@@ -43093,7 +43177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>2567</v>
       </c>
@@ -43143,7 +43227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>2570</v>
       </c>
@@ -43193,7 +43277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>2573</v>
       </c>
@@ -43243,7 +43327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>2577</v>
       </c>
@@ -43293,7 +43377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>2580</v>
       </c>
@@ -43343,7 +43427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>2583</v>
       </c>
@@ -43393,7 +43477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>2586</v>
       </c>
@@ -43443,7 +43527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>2590</v>
       </c>
@@ -43493,7 +43577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>2593</v>
       </c>
@@ -43543,7 +43627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>2597</v>
       </c>
@@ -43593,7 +43677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>2600</v>
       </c>
@@ -43643,7 +43727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>2603</v>
       </c>
@@ -43693,7 +43777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>2607</v>
       </c>
@@ -43743,7 +43827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>2611</v>
       </c>
@@ -43793,7 +43877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>2614</v>
       </c>
@@ -43843,7 +43927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>2618</v>
       </c>
@@ -43893,7 +43977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>2622</v>
       </c>
@@ -43943,7 +44027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>2626</v>
       </c>
@@ -43993,7 +44077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>2630</v>
       </c>
@@ -44043,7 +44127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>2634</v>
       </c>
@@ -44093,7 +44177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>2640</v>
       </c>
@@ -44143,7 +44227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>2644</v>
       </c>
@@ -44193,7 +44277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>2647</v>
       </c>
@@ -44243,7 +44327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>2651</v>
       </c>
@@ -44293,7 +44377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>2656</v>
       </c>
@@ -44343,7 +44427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
         <v>2659</v>
       </c>
@@ -44393,7 +44477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>2662</v>
       </c>
@@ -44443,7 +44527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
         <v>2666</v>
       </c>
@@ -44493,7 +44577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>2669</v>
       </c>
@@ -44543,7 +44627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
         <v>2672</v>
       </c>
@@ -44593,7 +44677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
         <v>2676</v>
       </c>
@@ -44643,7 +44727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
         <v>2679</v>
       </c>
@@ -44693,7 +44777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A668" t="s">
         <v>2683</v>
       </c>
@@ -44743,7 +44827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A669" t="s">
         <v>2687</v>
       </c>
@@ -44793,7 +44877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A670" t="s">
         <v>2691</v>
       </c>
@@ -44843,7 +44927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A671" t="s">
         <v>2695</v>
       </c>
@@ -44893,7 +44977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>2698</v>
       </c>
@@ -44943,7 +45027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A673" t="s">
         <v>2702</v>
       </c>
@@ -44993,7 +45077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>2705</v>
       </c>
@@ -45043,7 +45127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A675" t="s">
         <v>2709</v>
       </c>
@@ -45093,7 +45177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A676" t="s">
         <v>2712</v>
       </c>
@@ -45143,7 +45227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A677" t="s">
         <v>2716</v>
       </c>
@@ -45193,7 +45277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>2720</v>
       </c>
@@ -45243,7 +45327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A679" t="s">
         <v>2724</v>
       </c>
@@ -45293,7 +45377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A680" t="s">
         <v>2728</v>
       </c>
@@ -45343,7 +45427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A681" t="s">
         <v>2731</v>
       </c>
@@ -45393,7 +45477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A682" t="s">
         <v>2734</v>
       </c>
@@ -45443,7 +45527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A683" t="s">
         <v>2738</v>
       </c>
@@ -45493,7 +45577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A684" t="s">
         <v>2742</v>
       </c>
@@ -45543,7 +45627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A685" t="s">
         <v>2746</v>
       </c>
@@ -45593,7 +45677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>2749</v>
       </c>
@@ -45643,7 +45727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>2753</v>
       </c>
@@ -45693,7 +45777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>2757</v>
       </c>
@@ -45743,7 +45827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A689" t="s">
         <v>2760</v>
       </c>
@@ -45793,7 +45877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A690" t="s">
         <v>2764</v>
       </c>
@@ -45843,7 +45927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>2767</v>
       </c>
@@ -45893,7 +45977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A692" t="s">
         <v>2770</v>
       </c>
@@ -45943,7 +46027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>2774</v>
       </c>
@@ -45993,7 +46077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A694" t="s">
         <v>2778</v>
       </c>
@@ -46043,7 +46127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>2782</v>
       </c>
@@ -46093,7 +46177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A696" t="s">
         <v>2785</v>
       </c>
@@ -46143,7 +46227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A697" t="s">
         <v>2789</v>
       </c>
@@ -46193,7 +46277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A698" t="s">
         <v>2792</v>
       </c>
@@ -46243,7 +46327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A699" t="s">
         <v>2795</v>
       </c>
@@ -46293,7 +46377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A700" t="s">
         <v>2799</v>
       </c>
@@ -46343,7 +46427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="701" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A701" t="s">
         <v>2802</v>
       </c>
@@ -46393,7 +46477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="702" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A702" t="s">
         <v>2805</v>
       </c>
@@ -46443,7 +46527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="703" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A703" t="s">
         <v>2809</v>
       </c>
@@ -46493,7 +46577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="704" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>2812</v>
       </c>
@@ -46543,7 +46627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="705" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A705" t="s">
         <v>2816</v>
       </c>
@@ -46593,7 +46677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="706" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>2820</v>
       </c>
@@ -46643,7 +46727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="707" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>2823</v>
       </c>
@@ -46693,7 +46777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="708" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>2828</v>
       </c>
@@ -46743,7 +46827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="709" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>2832</v>
       </c>
@@ -46793,7 +46877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="710" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>2835</v>
       </c>
@@ -46843,7 +46927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="711" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A711" t="s">
         <v>2841</v>
       </c>
@@ -46893,7 +46977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="712" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A712" t="s">
         <v>2844</v>
       </c>
@@ -46943,7 +47027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="713" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>2847</v>
       </c>
@@ -46993,7 +47077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="714" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A714" t="s">
         <v>2850</v>
       </c>
@@ -47043,7 +47127,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="715" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A715" t="s">
         <v>2853</v>
       </c>
@@ -47093,7 +47177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="716" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A716" t="s">
         <v>2856</v>
       </c>
@@ -47143,7 +47227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="717" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A717" t="s">
         <v>2860</v>
       </c>
@@ -47193,7 +47277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="718" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A718" t="s">
         <v>2863</v>
       </c>
@@ -47243,7 +47327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="719" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A719" t="s">
         <v>2866</v>
       </c>
@@ -47293,7 +47377,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="720" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A720" t="s">
         <v>2869</v>
       </c>
@@ -47343,7 +47427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="721" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A721" t="s">
         <v>2873</v>
       </c>
@@ -47393,7 +47477,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="722" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A722" t="s">
         <v>2876</v>
       </c>
@@ -47443,7 +47527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="723" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A723" t="s">
         <v>2880</v>
       </c>
@@ -47493,7 +47577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="724" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A724" t="s">
         <v>2883</v>
       </c>
@@ -47543,7 +47627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="725" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A725" t="s">
         <v>2887</v>
       </c>
@@ -47587,7 +47671,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="726" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A726" t="s">
         <v>2893</v>
       </c>
@@ -47637,7 +47721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="727" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A727" t="s">
         <v>2896</v>
       </c>
@@ -47687,7 +47771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="728" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A728" t="s">
         <v>2899</v>
       </c>
@@ -47737,7 +47821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="729" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A729" t="s">
         <v>2902</v>
       </c>
@@ -47787,7 +47871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="730" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A730" t="s">
         <v>2905</v>
       </c>
@@ -47837,7 +47921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="731" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A731" t="s">
         <v>2908</v>
       </c>
@@ -47887,7 +47971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="732" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A732" t="s">
         <v>2911</v>
       </c>
@@ -47937,7 +48021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="733" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A733" t="s">
         <v>2915</v>
       </c>
@@ -47987,7 +48071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="734" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A734" t="s">
         <v>2918</v>
       </c>
@@ -48037,7 +48121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="735" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A735" t="s">
         <v>2922</v>
       </c>
@@ -48087,7 +48171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="736" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A736" t="s">
         <v>2925</v>
       </c>
@@ -48137,7 +48221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="737" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A737" t="s">
         <v>2929</v>
       </c>
@@ -48187,7 +48271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="738" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A738" t="s">
         <v>2931</v>
       </c>
@@ -48237,7 +48321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="739" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A739" t="s">
         <v>2934</v>
       </c>
@@ -48287,7 +48371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="740" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A740" t="s">
         <v>2938</v>
       </c>
@@ -48337,7 +48421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="741" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A741" t="s">
         <v>2941</v>
       </c>
@@ -48387,7 +48471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="742" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A742" t="s">
         <v>2944</v>
       </c>
@@ -48437,7 +48521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A743" t="s">
         <v>2947</v>
       </c>
@@ -48487,7 +48571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="744" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A744" t="s">
         <v>2950</v>
       </c>
@@ -48537,7 +48621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="745" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A745" t="s">
         <v>2954</v>
       </c>
@@ -48587,7 +48671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="746" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A746" t="s">
         <v>2957</v>
       </c>
@@ -48637,7 +48721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="747" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A747" t="s">
         <v>2960</v>
       </c>
@@ -48687,7 +48771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="748" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A748" t="s">
         <v>2963</v>
       </c>
@@ -48737,7 +48821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="749" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A749" t="s">
         <v>2967</v>
       </c>
@@ -48787,7 +48871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="750" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A750" t="s">
         <v>2970</v>
       </c>
@@ -48837,7 +48921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="751" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A751" t="s">
         <v>2974</v>
       </c>
@@ -48887,7 +48971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="752" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A752" t="s">
         <v>2978</v>
       </c>
@@ -48937,7 +49021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="753" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A753" t="s">
         <v>2982</v>
       </c>
@@ -48987,7 +49071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="754" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A754" t="s">
         <v>2984</v>
       </c>
@@ -49037,7 +49121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="755" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A755" t="s">
         <v>2988</v>
       </c>
@@ -49087,7 +49171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="756" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A756" t="s">
         <v>2992</v>
       </c>
@@ -49137,7 +49221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="757" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A757" t="s">
         <v>2995</v>
       </c>
@@ -49187,7 +49271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="758" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A758" t="s">
         <v>2998</v>
       </c>
@@ -49237,7 +49321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="759" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A759" t="s">
         <v>3001</v>
       </c>
@@ -49287,7 +49371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="760" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A760" t="s">
         <v>3004</v>
       </c>
@@ -49337,7 +49421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="761" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A761" t="s">
         <v>3009</v>
       </c>
@@ -49387,7 +49471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="762" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
         <v>3013</v>
       </c>
@@ -49437,7 +49521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="763" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A763" t="s">
         <v>3016</v>
       </c>
@@ -49487,7 +49571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="764" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
         <v>3019</v>
       </c>
@@ -49537,7 +49621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="765" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A765" t="s">
         <v>3022</v>
       </c>
@@ -49587,7 +49671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A766" t="s">
         <v>3026</v>
       </c>
@@ -49637,7 +49721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="767" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A767" t="s">
         <v>3030</v>
       </c>
@@ -49687,7 +49771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="768" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
         <v>3034</v>
       </c>
@@ -49737,7 +49821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="769" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
         <v>3038</v>
       </c>
@@ -49787,7 +49871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="770" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
         <v>3041</v>
       </c>
@@ -49837,7 +49921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="771" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
         <v>3044</v>
       </c>
@@ -49887,7 +49971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="772" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
         <v>3047</v>
       </c>
@@ -49937,7 +50021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="773" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A773" t="s">
         <v>3051</v>
       </c>
@@ -49987,7 +50071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="774" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
         <v>3054</v>
       </c>
@@ -50037,7 +50121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="775" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A775" t="s">
         <v>3058</v>
       </c>
@@ -50087,7 +50171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="776" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
         <v>3061</v>
       </c>
@@ -50137,7 +50221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="777" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A777" t="s">
         <v>3064</v>
       </c>
@@ -50187,7 +50271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="778" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A778" t="s">
         <v>3068</v>
       </c>
@@ -50237,7 +50321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="779" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A779" t="s">
         <v>3071</v>
       </c>
@@ -50287,7 +50371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="780" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A780" t="s">
         <v>3075</v>
       </c>
@@ -50337,7 +50421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="781" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A781" t="s">
         <v>3079</v>
       </c>
@@ -50387,7 +50471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="782" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A782" t="s">
         <v>3083</v>
       </c>
@@ -50437,7 +50521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="783" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A783" t="s">
         <v>3086</v>
       </c>
@@ -50487,7 +50571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="784" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
         <v>3089</v>
       </c>
@@ -50537,7 +50621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="785" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A785" t="s">
         <v>3092</v>
       </c>
@@ -50587,7 +50671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="786" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
         <v>3095</v>
       </c>
@@ -50637,7 +50721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="787" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A787" t="s">
         <v>3101</v>
       </c>
@@ -50687,7 +50771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="788" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A788" t="s">
         <v>3105</v>
       </c>
@@ -50737,7 +50821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="789" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
         <v>3109</v>
       </c>
@@ -50787,7 +50871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="790" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A790" t="s">
         <v>3113</v>
       </c>
@@ -50837,7 +50921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="791" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A791" t="s">
         <v>3116</v>
       </c>
@@ -50887,7 +50971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="792" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A792" t="s">
         <v>3120</v>
       </c>
@@ -50937,7 +51021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="793" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
         <v>3124</v>
       </c>
@@ -50987,7 +51071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="794" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A794" t="s">
         <v>3128</v>
       </c>
@@ -51037,7 +51121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="795" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A795" t="s">
         <v>3132</v>
       </c>
@@ -51087,7 +51171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="796" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A796" t="s">
         <v>3134</v>
       </c>
@@ -51137,7 +51221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="797" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A797" t="s">
         <v>3137</v>
       </c>
@@ -51187,7 +51271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="798" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
         <v>3141</v>
       </c>
@@ -51237,7 +51321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="799" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
         <v>3145</v>
       </c>
@@ -51287,7 +51371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="800" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A800" t="s">
         <v>3149</v>
       </c>
@@ -51337,7 +51421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="801" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A801" t="s">
         <v>3153</v>
       </c>
@@ -51387,7 +51471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="802" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A802" t="s">
         <v>3157</v>
       </c>
@@ -51437,7 +51521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="803" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A803" t="s">
         <v>3160</v>
       </c>
@@ -51487,7 +51571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="804" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A804" t="s">
         <v>3164</v>
       </c>
@@ -51537,7 +51621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="805" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A805" t="s">
         <v>3167</v>
       </c>
@@ -51587,7 +51671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="806" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A806" t="s">
         <v>3171</v>
       </c>
@@ -51637,7 +51721,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="807" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A807" t="s">
         <v>3175</v>
       </c>
@@ -51687,7 +51771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="808" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A808" t="s">
         <v>3179</v>
       </c>
@@ -51737,7 +51821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="809" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A809" t="s">
         <v>3183</v>
       </c>
@@ -51787,7 +51871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="810" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A810" t="s">
         <v>3187</v>
       </c>
@@ -51837,7 +51921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="811" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A811" t="s">
         <v>3191</v>
       </c>
@@ -51887,7 +51971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="812" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A812" t="s">
         <v>3194</v>
       </c>
@@ -51931,7 +52015,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="813" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A813" t="s">
         <v>3200</v>
       </c>
@@ -51981,7 +52065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="814" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A814" t="s">
         <v>3207</v>
       </c>
@@ -52031,7 +52115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="815" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A815" t="s">
         <v>3210</v>
       </c>
@@ -52081,7 +52165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="816" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A816" t="s">
         <v>3214</v>
       </c>
@@ -52131,7 +52215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="817" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A817" t="s">
         <v>3218</v>
       </c>
@@ -52181,7 +52265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="818" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
         <v>3222</v>
       </c>
@@ -52231,7 +52315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="819" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A819" t="s">
         <v>3226</v>
       </c>
@@ -52281,7 +52365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="820" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A820" t="s">
         <v>3230</v>
       </c>
@@ -52331,7 +52415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="821" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A821" t="s">
         <v>3233</v>
       </c>
@@ -52381,7 +52465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="822" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A822" t="s">
         <v>3236</v>
       </c>
@@ -52431,7 +52515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="823" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A823" t="s">
         <v>3239</v>
       </c>
@@ -52481,7 +52565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="824" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A824" t="s">
         <v>3244</v>
       </c>
@@ -52531,7 +52615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="825" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A825" t="s">
         <v>3248</v>
       </c>
@@ -52581,7 +52665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="826" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A826" t="s">
         <v>3251</v>
       </c>
@@ -52631,7 +52715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="827" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A827" t="s">
         <v>3255</v>
       </c>
@@ -52681,7 +52765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="828" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A828" t="s">
         <v>3259</v>
       </c>
@@ -52731,7 +52815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="829" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A829" t="s">
         <v>3263</v>
       </c>
@@ -52781,7 +52865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="830" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A830" t="s">
         <v>3266</v>
       </c>
@@ -52831,7 +52915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="831" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A831" t="s">
         <v>3269</v>
       </c>
@@ -52881,7 +52965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A832" t="s">
         <v>3272</v>
       </c>
@@ -52931,7 +53015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="833" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A833" t="s">
         <v>3276</v>
       </c>
@@ -52981,7 +53065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="834" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A834" t="s">
         <v>3281</v>
       </c>
@@ -53031,7 +53115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="835" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A835" t="s">
         <v>3284</v>
       </c>
@@ -53081,7 +53165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="836" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A836" t="s">
         <v>3288</v>
       </c>
@@ -53131,7 +53215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="837" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A837" t="s">
         <v>3291</v>
       </c>
@@ -53181,7 +53265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="838" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A838" t="s">
         <v>3295</v>
       </c>
@@ -53231,7 +53315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="839" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A839" t="s">
         <v>3299</v>
       </c>
@@ -53281,7 +53365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="840" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A840" t="s">
         <v>3302</v>
       </c>
@@ -53331,7 +53415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="841" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A841" t="s">
         <v>3305</v>
       </c>
@@ -53381,7 +53465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="842" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A842" t="s">
         <v>3309</v>
       </c>
@@ -53431,7 +53515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="843" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A843" t="s">
         <v>3313</v>
       </c>
@@ -53481,7 +53565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="844" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A844" t="s">
         <v>3319</v>
       </c>
@@ -53531,7 +53615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="845" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A845" t="s">
         <v>3322</v>
       </c>
@@ -53581,7 +53665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="846" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A846" t="s">
         <v>3326</v>
       </c>
@@ -53631,7 +53715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="847" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A847" t="s">
         <v>3329</v>
       </c>
@@ -53681,7 +53765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="848" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A848" t="s">
         <v>3332</v>
       </c>
@@ -53731,7 +53815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="849" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A849" t="s">
         <v>3336</v>
       </c>
@@ -53781,7 +53865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="850" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A850" t="s">
         <v>3340</v>
       </c>
@@ -53831,7 +53915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="851" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A851" t="s">
         <v>3343</v>
       </c>
@@ -53881,7 +53965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="852" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A852" t="s">
         <v>3346</v>
       </c>
@@ -53931,7 +54015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="853" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A853" t="s">
         <v>3349</v>
       </c>
@@ -53981,7 +54065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="854" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A854" t="s">
         <v>3354</v>
       </c>
@@ -54031,7 +54115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="855" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A855" t="s">
         <v>3358</v>
       </c>
@@ -54081,7 +54165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="856" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A856" t="s">
         <v>3362</v>
       </c>
@@ -54131,7 +54215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="857" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A857" t="s">
         <v>3365</v>
       </c>
@@ -54181,7 +54265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="858" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A858" t="s">
         <v>3368</v>
       </c>
@@ -54231,7 +54315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="859" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A859" t="s">
         <v>3372</v>
       </c>
@@ -54281,7 +54365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="860" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A860" t="s">
         <v>3376</v>
       </c>
@@ -54331,7 +54415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="861" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>3379</v>
       </c>
@@ -54381,7 +54465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="862" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>3382</v>
       </c>
@@ -54431,7 +54515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="863" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A863" t="s">
         <v>3385</v>
       </c>
@@ -54481,7 +54565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="864" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A864" t="s">
         <v>3391</v>
       </c>
@@ -54531,7 +54615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="865" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A865" t="s">
         <v>3394</v>
       </c>
@@ -54581,7 +54665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="866" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>3397</v>
       </c>
@@ -54631,7 +54715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="867" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A867" t="s">
         <v>3400</v>
       </c>
@@ -54681,7 +54765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="868" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>3403</v>
       </c>
@@ -54731,7 +54815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="869" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>3406</v>
       </c>
@@ -54781,7 +54865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="870" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>3409</v>
       </c>
@@ -54831,7 +54915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="871" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A871" t="s">
         <v>3413</v>
       </c>
@@ -54881,7 +54965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="872" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A872" t="s">
         <v>3416</v>
       </c>
@@ -54931,7 +55015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="873" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A873" t="s">
         <v>3420</v>
       </c>
@@ -54981,7 +55065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="874" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>3424</v>
       </c>
@@ -55031,7 +55115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="875" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>3428</v>
       </c>
@@ -55081,7 +55165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="876" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A876" t="s">
         <v>3432</v>
       </c>
@@ -55131,7 +55215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="877" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A877" t="s">
         <v>3436</v>
       </c>
@@ -55181,7 +55265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="878" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A878" t="s">
         <v>3439</v>
       </c>
@@ -55231,7 +55315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="879" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A879" t="s">
         <v>3442</v>
       </c>
@@ -55281,7 +55365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="880" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A880" t="s">
         <v>3445</v>
       </c>
@@ -55331,7 +55415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="881" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A881" t="s">
         <v>3448</v>
       </c>
@@ -55381,7 +55465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="882" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A882" t="s">
         <v>3451</v>
       </c>
@@ -55431,7 +55515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="883" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A883" t="s">
         <v>3454</v>
       </c>
@@ -55481,7 +55565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="884" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A884" t="s">
         <v>3459</v>
       </c>
@@ -55531,7 +55615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="885" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A885" t="s">
         <v>3463</v>
       </c>
@@ -55581,7 +55665,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="886" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A886" t="s">
         <v>3467</v>
       </c>
@@ -55631,7 +55715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="887" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A887" t="s">
         <v>3471</v>
       </c>
@@ -55681,7 +55765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="888" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A888" t="s">
         <v>3475</v>
       </c>
@@ -55731,7 +55815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="889" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A889" t="s">
         <v>3478</v>
       </c>
@@ -55781,7 +55865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="890" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A890" t="s">
         <v>3482</v>
       </c>
@@ -55831,7 +55915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="891" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A891" t="s">
         <v>3486</v>
       </c>
@@ -55881,7 +55965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="892" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A892" t="s">
         <v>3490</v>
       </c>
@@ -55931,7 +56015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="893" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A893" t="s">
         <v>3493</v>
       </c>
@@ -55981,7 +56065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="894" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A894" t="s">
         <v>3496</v>
       </c>
@@ -56031,7 +56115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="895" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A895" t="s">
         <v>3500</v>
       </c>
@@ -56081,7 +56165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="896" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A896" t="s">
         <v>3503</v>
       </c>
@@ -56131,7 +56215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="897" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A897" t="s">
         <v>3506</v>
       </c>
@@ -56181,7 +56265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="898" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A898" t="s">
         <v>3510</v>
       </c>
@@ -56231,7 +56315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="899" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A899" t="s">
         <v>3513</v>
       </c>
@@ -56281,7 +56365,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="900" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A900" t="s">
         <v>3517</v>
       </c>
@@ -56331,7 +56415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="901" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A901" t="s">
         <v>3521</v>
       </c>
@@ -56381,7 +56465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="902" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A902" t="s">
         <v>3524</v>
       </c>
@@ -56431,7 +56515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="903" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A903" t="s">
         <v>3528</v>
       </c>
@@ -56475,7 +56559,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="904" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A904" t="s">
         <v>3534</v>
       </c>
@@ -56519,7 +56603,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="905" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A905" t="s">
         <v>3540</v>
       </c>
@@ -56563,7 +56647,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="906" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A906" t="s">
         <v>3546</v>
       </c>
@@ -56610,7 +56694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="907" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A907" t="s">
         <v>3552</v>
       </c>
@@ -56657,7 +56741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="908" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A908" t="s">
         <v>3555</v>
       </c>
@@ -56704,7 +56788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="909" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A909" t="s">
         <v>3558</v>
       </c>
@@ -56751,7 +56835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="910" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A910" t="s">
         <v>3561</v>
       </c>
@@ -56798,7 +56882,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="911" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A911" t="s">
         <v>3564</v>
       </c>
@@ -56845,7 +56929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="912" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A912" t="s">
         <v>3567</v>
       </c>
@@ -56892,7 +56976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="913" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A913" t="s">
         <v>3570</v>
       </c>
@@ -56939,7 +57023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="914" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A914" t="s">
         <v>3573</v>
       </c>
@@ -56986,7 +57070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="915" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A915" t="s">
         <v>3576</v>
       </c>
@@ -57033,7 +57117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="916" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A916" t="s">
         <v>3579</v>
       </c>
@@ -57080,7 +57164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="917" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A917" t="s">
         <v>3584</v>
       </c>
@@ -57127,7 +57211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="918" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A918" t="s">
         <v>3587</v>
       </c>
@@ -57174,7 +57258,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="919" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A919" t="s">
         <v>3590</v>
       </c>
@@ -57221,7 +57305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="920" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A920" t="s">
         <v>3593</v>
       </c>
@@ -57268,7 +57352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="921" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A921" t="s">
         <v>3596</v>
       </c>
@@ -57315,7 +57399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="922" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A922" t="s">
         <v>3599</v>
       </c>
@@ -57362,7 +57446,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="923" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A923" t="s">
         <v>3602</v>
       </c>
@@ -57409,7 +57493,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="924" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A924" t="s">
         <v>3605</v>
       </c>
@@ -57456,7 +57540,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="925" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A925" t="s">
         <v>3608</v>
       </c>
@@ -57503,7 +57587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="926" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A926" t="s">
         <v>3611</v>
       </c>
@@ -57550,7 +57634,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="927" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A927" t="s">
         <v>3616</v>
       </c>
@@ -57597,7 +57681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="928" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A928" t="s">
         <v>3619</v>
       </c>
@@ -57644,7 +57728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="929" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A929" t="s">
         <v>3622</v>
       </c>
@@ -57691,7 +57775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="930" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A930" t="s">
         <v>3625</v>
       </c>
@@ -57738,7 +57822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="931" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A931" t="s">
         <v>3628</v>
       </c>
@@ -57785,7 +57869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="932" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A932" t="s">
         <v>3631</v>
       </c>
@@ -57832,7 +57916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="933" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A933" t="s">
         <v>3634</v>
       </c>
@@ -57879,7 +57963,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="934" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A934" t="s">
         <v>3637</v>
       </c>
@@ -57926,7 +58010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="935" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A935" t="s">
         <v>3640</v>
       </c>
@@ -57973,7 +58057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="936" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A936" t="s">
         <v>3643</v>
       </c>
@@ -58023,7 +58107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="937" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A937" t="s">
         <v>3648</v>
       </c>
@@ -58073,7 +58157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="938" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A938" t="s">
         <v>3651</v>
       </c>
@@ -58123,7 +58207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="939" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A939" t="s">
         <v>3655</v>
       </c>
@@ -58173,7 +58257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="940" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A940" t="s">
         <v>3658</v>
       </c>
@@ -58223,7 +58307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="941" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A941" t="s">
         <v>3661</v>
       </c>
@@ -58273,7 +58357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="942" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A942" t="s">
         <v>3664</v>
       </c>
@@ -58323,7 +58407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="943" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A943" t="s">
         <v>3667</v>
       </c>
@@ -58373,7 +58457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="944" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A944" t="s">
         <v>3670</v>
       </c>
@@ -58423,7 +58507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="945" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A945" t="s">
         <v>3673</v>
       </c>
@@ -58473,7 +58557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="946" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A946" t="s">
         <v>3676</v>
       </c>
@@ -58523,7 +58607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="947" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A947" t="s">
         <v>3679</v>
       </c>
@@ -58573,7 +58657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="948" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A948" t="s">
         <v>3682</v>
       </c>
@@ -58623,7 +58707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="949" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A949" t="s">
         <v>3685</v>
       </c>
@@ -58673,7 +58757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="950" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A950" t="s">
         <v>3690</v>
       </c>
@@ -58723,7 +58807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="951" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A951" t="s">
         <v>3692</v>
       </c>
@@ -58773,7 +58857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="952" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A952" t="s">
         <v>3695</v>
       </c>
@@ -58823,7 +58907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="953" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A953" t="s">
         <v>3699</v>
       </c>
@@ -58873,7 +58957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="954" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A954" t="s">
         <v>3702</v>
       </c>
@@ -58923,7 +59007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="955" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A955" t="s">
         <v>3705</v>
       </c>
@@ -58973,7 +59057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="956" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A956" t="s">
         <v>3708</v>
       </c>
@@ -59023,7 +59107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="957" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A957" t="s">
         <v>3711</v>
       </c>
@@ -59073,7 +59157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="958" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A958" t="s">
         <v>3714</v>
       </c>
@@ -59123,7 +59207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="959" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A959" t="s">
         <v>3717</v>
       </c>
@@ -59173,7 +59257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="960" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A960" t="s">
         <v>3721</v>
       </c>
@@ -59223,7 +59307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="961" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A961" t="s">
         <v>3724</v>
       </c>
@@ -59273,7 +59357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="962" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A962" t="s">
         <v>3727</v>
       </c>
@@ -59323,7 +59407,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="963" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A963" t="s">
         <v>3732</v>
       </c>
@@ -59373,7 +59457,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="964" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A964" t="s">
         <v>3736</v>
       </c>
@@ -59423,7 +59507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="965" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A965" t="s">
         <v>3739</v>
       </c>
@@ -59473,7 +59557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="966" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A966" t="s">
         <v>3742</v>
       </c>
@@ -59523,7 +59607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="967" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A967" t="s">
         <v>3746</v>
       </c>
@@ -59573,7 +59657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="968" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A968" t="s">
         <v>3749</v>
       </c>
@@ -59623,7 +59707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="969" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A969" t="s">
         <v>3752</v>
       </c>
@@ -59673,7 +59757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="970" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A970" t="s">
         <v>3755</v>
       </c>
@@ -59723,7 +59807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="971" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A971" t="s">
         <v>3758</v>
       </c>
@@ -59773,7 +59857,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="972" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A972" t="s">
         <v>3761</v>
       </c>
@@ -59823,7 +59907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="973" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A973" t="s">
         <v>3768</v>
       </c>
@@ -59873,7 +59957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="974" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A974" t="s">
         <v>3771</v>
       </c>
@@ -59923,7 +60007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="975" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A975" t="s">
         <v>3775</v>
       </c>
@@ -59973,7 +60057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="976" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A976" t="s">
         <v>3779</v>
       </c>
@@ -60023,7 +60107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="977" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A977" t="s">
         <v>3782</v>
       </c>
@@ -60073,7 +60157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="978" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A978" t="s">
         <v>3785</v>
       </c>
@@ -60123,7 +60207,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="979" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A979" t="s">
         <v>3788</v>
       </c>
@@ -60173,7 +60257,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="980" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A980" t="s">
         <v>3792</v>
       </c>
@@ -60223,7 +60307,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="981" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A981" t="s">
         <v>3795</v>
       </c>
@@ -60273,7 +60357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="982" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A982" t="s">
         <v>3798</v>
       </c>
@@ -60305,7 +60389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="983" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A983" t="s">
         <v>3800</v>
       </c>
@@ -60334,7 +60418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="984" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A984" t="s">
         <v>3802</v>
       </c>
@@ -60363,7 +60447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="985" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A985" t="s">
         <v>3803</v>
       </c>
@@ -60392,7 +60476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="986" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A986" t="s">
         <v>3804</v>
       </c>
@@ -60421,7 +60505,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="987" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A987" t="s">
         <v>3805</v>
       </c>
@@ -60450,7 +60534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="988" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A988" t="s">
         <v>3806</v>
       </c>
@@ -60479,7 +60563,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="989" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A989" t="s">
         <v>3807</v>
       </c>
@@ -60508,7 +60592,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="990" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A990" t="s">
         <v>3808</v>
       </c>
@@ -60537,7 +60621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="991" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A991" t="s">
         <v>3809</v>
       </c>

--- a/STARTREK.xlsx
+++ b/STARTREK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4A104E-7468-4BA8-BC9D-A9949368A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44313958-D358-4924-8AA0-979F7091E37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10671" uniqueCount="3822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10673" uniqueCount="3824">
   <si>
     <t>id</t>
   </si>
@@ -11489,6 +11489,12 @@
   </si>
   <si>
     <t>2179.3</t>
+  </si>
+  <si>
+    <t>2355.6</t>
+  </si>
+  <si>
+    <t>2873.2</t>
   </si>
 </sst>
 </file>
@@ -19952,8 +19958,17 @@
       <c r="F168" t="s">
         <v>682</v>
       </c>
+      <c r="G168">
+        <v>49</v>
+      </c>
       <c r="H168" s="1">
         <v>46282</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>3822</v>
+      </c>
+      <c r="J168">
+        <v>2262</v>
       </c>
       <c r="K168" t="s">
         <v>21</v>
@@ -19993,8 +20008,17 @@
       <c r="F169" t="s">
         <v>685</v>
       </c>
+      <c r="G169">
+        <v>62</v>
+      </c>
       <c r="H169" s="1">
         <v>46289</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>3823</v>
+      </c>
+      <c r="J169">
+        <v>2262</v>
       </c>
       <c r="K169" t="s">
         <v>21</v>
